--- a/data/trans_dic/P16A05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,05</t>
+          <t>3,44; 6,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,15</t>
+          <t>3,73; 6,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,77</t>
+          <t>3,62; 6,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 10,95</t>
+          <t>6,44; 11,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 9,73</t>
+          <t>6,86; 9,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 12,81</t>
+          <t>9,3; 12,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,91</t>
+          <t>10,56; 15,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 20,56</t>
+          <t>15,87; 20,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,63</t>
+          <t>5,58; 7,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,85</t>
+          <t>7,36; 9,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,85</t>
+          <t>8,1; 10,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,62; 16,03</t>
+          <t>12,6; 15,94</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,2</t>
+          <t>0,92; 2,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,28</t>
+          <t>1,87; 3,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,0</t>
+          <t>2,43; 3,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,62</t>
+          <t>2,41; 4,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,65</t>
+          <t>2,93; 4,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,36</t>
+          <t>4,11; 6,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,75</t>
+          <t>5,45; 7,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,15</t>
+          <t>4,39; 7,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,22</t>
+          <t>2,02; 3,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,47</t>
+          <t>3,17; 4,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 5,56</t>
+          <t>4,19; 5,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,57</t>
+          <t>3,73; 5,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,1</t>
+          <t>1,31; 4,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,85</t>
+          <t>1,59; 5,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,65</t>
+          <t>1,53; 4,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,84</t>
+          <t>1,53; 3,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,68</t>
+          <t>1,43; 4,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,96</t>
+          <t>2,24; 5,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,36</t>
+          <t>1,36; 4,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,66</t>
+          <t>2,25; 4,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,86</t>
+          <t>1,77; 3,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,98</t>
+          <t>2,32; 4,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,72</t>
+          <t>1,74; 3,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,74</t>
+          <t>2,12; 3,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,21</t>
+          <t>2,07; 3,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,14</t>
+          <t>2,72; 4,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,12</t>
+          <t>2,93; 4,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 4,9</t>
+          <t>3,18; 4,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,14</t>
+          <t>4,6; 6,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,12</t>
+          <t>6,31; 8,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,54</t>
+          <t>6,71; 8,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,91</t>
+          <t>6,69; 8,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,54</t>
+          <t>3,5; 4,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 5,93</t>
+          <t>4,81; 5,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,23</t>
+          <t>5,1; 6,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,77</t>
+          <t>5,24; 6,8</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36009; 62409</t>
+          <t>35518; 62943</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38383; 69653</t>
+          <t>36359; 66557</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28187; 51089</t>
+          <t>27322; 50390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32964; 56213</t>
+          <t>33079; 56583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>87273; 127914</t>
+          <t>90176; 129397</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>124773; 170796</t>
+          <t>124027; 168739</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>104893; 148286</t>
+          <t>105066; 149605</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>120428; 154412</t>
+          <t>119169; 155766</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>132746; 179097</t>
+          <t>131057; 178991</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170575; 227253</t>
+          <t>169791; 226839</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140534; 189780</t>
+          <t>141743; 188407</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>159647; 202732</t>
+          <t>159354; 201538</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16771; 37225</t>
+          <t>15491; 35465</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34964; 64345</t>
+          <t>36586; 66638</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50609; 83135</t>
+          <t>50493; 82485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56482; 105732</t>
+          <t>55197; 102499</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45522; 73769</t>
+          <t>46597; 75472</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72398; 111447</t>
+          <t>72015; 110992</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>109037; 154044</t>
+          <t>108459; 152549</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94921; 159846</t>
+          <t>98167; 157596</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68630; 105587</t>
+          <t>66253; 103075</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115776; 165741</t>
+          <t>117714; 166317</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168669; 225908</t>
+          <t>170299; 224961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>175660; 252400</t>
+          <t>168841; 248993</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7492; 22617</t>
+          <t>7215; 23441</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7469; 28118</t>
+          <t>7661; 28502</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8707; 25444</t>
+          <t>8369; 24444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9663; 24837</t>
+          <t>9899; 24856</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7279; 22314</t>
+          <t>6811; 22031</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10206; 27278</t>
+          <t>10235; 26117</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7532; 23948</t>
+          <t>7484; 23500</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15536; 30798</t>
+          <t>14853; 30337</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18323; 39708</t>
+          <t>18170; 39940</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20542; 46668</t>
+          <t>21753; 46540</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17783; 40734</t>
+          <t>19070; 41040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27655; 48901</t>
+          <t>27774; 47625</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68210; 105061</t>
+          <t>67807; 103312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93928; 141185</t>
+          <t>92701; 140391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96907; 139321</t>
+          <t>98844; 141428</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>109253; 168898</t>
+          <t>109703; 168625</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>155861; 207406</t>
+          <t>155481; 207452</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>222978; 287626</t>
+          <t>223635; 289398</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>238967; 301785</t>
+          <t>237089; 301298</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>240087; 325034</t>
+          <t>244182; 326008</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>235596; 301929</t>
+          <t>233080; 297133</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>330466; 412330</t>
+          <t>334621; 409433</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>351175; 430577</t>
+          <t>352521; 431323</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>374744; 480565</t>
+          <t>371949; 482741</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,1</t>
+          <t>3,36; 5,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,83</t>
+          <t>3,72; 7,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,68</t>
+          <t>3,65; 6,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,02</t>
+          <t>6,34; 10,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 9,84</t>
+          <t>6,73; 9,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 12,65</t>
+          <t>9,47; 12,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,56; 15,04</t>
+          <t>10,54; 15,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,87; 20,74</t>
+          <t>15,6; 19,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 7,63</t>
+          <t>5,61; 7,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 9,83</t>
+          <t>7,33; 9,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 10,77</t>
+          <t>7,98; 10,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,94</t>
+          <t>12,41; 15,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,1</t>
+          <t>0,94; 2,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,4</t>
+          <t>1,82; 3,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,97</t>
+          <t>2,48; 4,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,48</t>
+          <t>3,14; 4,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,75</t>
+          <t>2,86; 4,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,34</t>
+          <t>4,11; 6,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,67</t>
+          <t>5,41; 7,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,04</t>
+          <t>5,92; 7,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,14</t>
+          <t>2,01; 3,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 4,48</t>
+          <t>3,16; 4,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 5,53</t>
+          <t>4,09; 5,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,5</t>
+          <t>4,72; 5,96</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,25</t>
+          <t>1,31; 4,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,93</t>
+          <t>1,58; 5,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,47</t>
+          <t>1,48; 4,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,84</t>
+          <t>1,33; 3,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,62</t>
+          <t>1,55; 4,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,71</t>
+          <t>2,02; 5,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,28</t>
+          <t>1,31; 4,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,59</t>
+          <t>2,37; 4,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,89</t>
+          <t>1,74; 3,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,96</t>
+          <t>2,32; 4,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,74</t>
+          <t>1,75; 3,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,64</t>
+          <t>2,08; 3,58</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,15</t>
+          <t>2,11; 3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,11</t>
+          <t>2,75; 4,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,19</t>
+          <t>2,88; 4,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,89</t>
+          <t>3,68; 5,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,14</t>
+          <t>4,53; 6,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,17</t>
+          <t>6,29; 8,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,53</t>
+          <t>6,73; 8,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 8,93</t>
+          <t>7,7; 9,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,46</t>
+          <t>3,49; 4,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 5,88</t>
+          <t>4,73; 5,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 6,24</t>
+          <t>5,07; 6,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,8</t>
+          <t>5,91; 6,9</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>135395</t>
+          <t>143750</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>178804</t>
+          <t>191600</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35518; 62943</t>
+          <t>34667; 60346</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36359; 66557</t>
+          <t>36203; 68802</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27322; 50390</t>
+          <t>27517; 51139</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33079; 56583</t>
+          <t>36571; 60393</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>90176; 129397</t>
+          <t>88494; 128729</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>124027; 168739</t>
+          <t>126299; 172598</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>105066; 149605</t>
+          <t>104852; 149992</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>119169; 155766</t>
+          <t>127819; 160743</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>131057; 178991</t>
+          <t>131767; 178188</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>169791; 226839</t>
+          <t>169173; 225195</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>141743; 188407</t>
+          <t>139566; 190312</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>159354; 201538</t>
+          <t>173317; 213315</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82411</t>
+          <t>86634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>133316</t>
+          <t>145546</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>215726</t>
+          <t>232179</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15491; 35465</t>
+          <t>15985; 36248</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36586; 66638</t>
+          <t>35615; 65621</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50493; 82485</t>
+          <t>51537; 83622</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55197; 102499</t>
+          <t>69935; 108025</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46597; 75472</t>
+          <t>45381; 75664</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72015; 110992</t>
+          <t>71942; 111821</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>108459; 152549</t>
+          <t>107600; 152151</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>98167; 157596</t>
+          <t>128448; 165578</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66253; 103075</t>
+          <t>66052; 104301</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117714; 166317</t>
+          <t>117420; 164909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>170299; 224961</t>
+          <t>166307; 223278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>168841; 248993</t>
+          <t>207667; 262272</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15894</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>40080</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7215; 23441</t>
+          <t>7200; 22197</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7661; 28502</t>
+          <t>7589; 27289</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8369; 24444</t>
+          <t>8103; 24433</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9899; 24856</t>
+          <t>9461; 24935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6811; 22031</t>
+          <t>7400; 21440</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10235; 26117</t>
+          <t>9244; 25405</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7484; 23500</t>
+          <t>7192; 22493</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14853; 30337</t>
+          <t>17409; 33355</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18170; 39940</t>
+          <t>17928; 39273</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21753; 46540</t>
+          <t>21737; 46368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19070; 41040</t>
+          <t>19160; 41421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27774; 47625</t>
+          <t>30151; 51818</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>290297</t>
+          <t>313418</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>432011</t>
+          <t>463859</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67807; 103312</t>
+          <t>69233; 104896</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92701; 140391</t>
+          <t>93771; 138864</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98844; 141428</t>
+          <t>97214; 141966</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>109703; 168625</t>
+          <t>129390; 176938</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>155481; 207452</t>
+          <t>153029; 205573</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>223635; 289398</t>
+          <t>222892; 286053</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>237089; 301298</t>
+          <t>237690; 304094</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>244182; 326008</t>
+          <t>286810; 339713</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>233080; 297133</t>
+          <t>232017; 294823</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>334621; 409433</t>
+          <t>329202; 409903</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>352521; 431323</t>
+          <t>350284; 425110</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>371949; 482741</t>
+          <t>427780; 499560</t>
         </is>
       </c>
     </row>
